--- a/测试集/泛用性验收_v3/W2/W2_预期_全年更新.xlsx
+++ b/测试集/泛用性验收_v3/W2/W2_预期_全年更新.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,26 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +52,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,77 +442,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>责任单位</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>任务名称</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>1月</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2月</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>3月</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>4月</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>9月</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>11月</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>12月</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
@@ -501,44 +526,44 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>完成年度预算</t>
+          <t>完成年度预算编制</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>34</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H2" t="n">
         <v>8</v>
       </c>
-      <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G2" t="n">
-        <v>19</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40</v>
-      </c>
       <c r="I2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="K2" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M2" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="N2" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="O2">
         <f>SUM(C2:N2)</f>
@@ -553,44 +578,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>组织安全培训</t>
+          <t>组织安全培训演练</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3" t="n">
         <v>9</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G3" t="n">
         <v>32</v>
       </c>
-      <c r="F3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" t="n">
-        <v>13</v>
-      </c>
       <c r="H3" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K3" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="M3" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="O3">
         <f>SUM(C3:N3)</f>
@@ -609,40 +634,40 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="n">
         <v>22</v>
       </c>
-      <c r="E4" t="n">
-        <v>30</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>9</v>
-      </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="J4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M4" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="N4" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="O4">
         <f>SUM(C4:N4)</f>
@@ -661,40 +686,40 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I5" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J5" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K5" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="M5" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="N5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="O5">
         <f>SUM(C5:N5)</f>
@@ -709,44 +734,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>完成年度预算</t>
+          <t>组织安全培训演练</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="D6" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I6" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J6" t="n">
         <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="N6" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="O6">
         <f>SUM(C6:N6)</f>
@@ -761,44 +786,44 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>组织安全培训</t>
+          <t>设备巡检维护</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="E7" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="K7" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M7" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="O7">
         <f>SUM(C7:N7)</f>
@@ -813,44 +838,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>设备巡检维护</t>
+          <t>季度报表汇总</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="I8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18</v>
+      </c>
+      <c r="K8" t="n">
+        <v>46</v>
+      </c>
+      <c r="L8" t="n">
+        <v>16</v>
+      </c>
+      <c r="M8" t="n">
         <v>23</v>
       </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>49</v>
-      </c>
-      <c r="L8" t="n">
-        <v>37</v>
-      </c>
-      <c r="M8" t="n">
-        <v>24</v>
-      </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O8">
         <f>SUM(C8:N8)</f>
@@ -865,44 +890,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>季度报表汇总</t>
+          <t>完成资料汇总</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="H9" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I9" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M9" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="N9" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <f>SUM(C9:N9)</f>
@@ -917,44 +942,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>完成年度预算</t>
+          <t>设备巡检维护</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I10" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="N10" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="O10">
         <f>SUM(C10:N10)</f>
@@ -969,44 +994,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>组织安全培训</t>
+          <t>季度报表汇总</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="H11" t="n">
+        <v>23</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
         <v>49</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>24</v>
-      </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="L11" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="M11" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="O11">
         <f>SUM(C11:N11)</f>
@@ -1021,44 +1046,44 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>设备巡检维护</t>
+          <t>完成资料汇总</t>
         </is>
       </c>
       <c r="C12" t="n">
+        <v>47</v>
+      </c>
+      <c r="D12" t="n">
+        <v>33</v>
+      </c>
+      <c r="E12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F12" t="n">
+        <v>33</v>
+      </c>
+      <c r="G12" t="n">
+        <v>39</v>
+      </c>
+      <c r="H12" t="n">
+        <v>49</v>
+      </c>
+      <c r="I12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J12" t="n">
         <v>29</v>
       </c>
-      <c r="D12" t="n">
-        <v>46</v>
-      </c>
-      <c r="E12" t="n">
-        <v>21</v>
-      </c>
-      <c r="F12" t="n">
-        <v>42</v>
-      </c>
-      <c r="G12" t="n">
-        <v>12</v>
-      </c>
-      <c r="H12" t="n">
-        <v>44</v>
-      </c>
-      <c r="I12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J12" t="n">
-        <v>41</v>
-      </c>
       <c r="K12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L12" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="M12" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="N12" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="O12">
         <f>SUM(C12:N12)</f>
@@ -1073,44 +1098,44 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>季度报表汇总</t>
+          <t>成本合计核算</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="n">
         <v>47</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" t="n">
+        <v>29</v>
+      </c>
+      <c r="L13" t="n">
+        <v>40</v>
+      </c>
+      <c r="M13" t="n">
+        <v>29</v>
+      </c>
+      <c r="N13" t="n">
         <v>42</v>
-      </c>
-      <c r="J13" t="n">
-        <v>16</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L13" t="n">
-        <v>32</v>
-      </c>
-      <c r="M13" t="n">
-        <v>25</v>
-      </c>
-      <c r="N13" t="n">
-        <v>50</v>
       </c>
       <c r="O13">
         <f>SUM(C13:N13)</f>

--- a/测试集/泛用性验收_v3/W2/W2_预期_全年更新.xlsx
+++ b/测试集/泛用性验收_v3/W2/W2_预期_全年更新.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全年" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度计划" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -70,9 +74,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,136 +445,95 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>各单位月度任务数量分配表</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
           <t>责任单位</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>任务名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>1月</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>2月</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>3月</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>4月</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>9月</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>11月</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>12月</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>综合办公室</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>完成年度预算编制</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>34</v>
-      </c>
-      <c r="D2" t="n">
-        <v>46</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J2" t="n">
-        <v>36</v>
-      </c>
-      <c r="K2" t="n">
-        <v>10</v>
-      </c>
-      <c r="L2" t="n">
-        <v>14</v>
-      </c>
-      <c r="M2" t="n">
-        <v>7</v>
-      </c>
-      <c r="N2" t="n">
-        <v>25</v>
-      </c>
-      <c r="O2">
-        <f>SUM(C2:N2)</f>
-        <v/>
       </c>
     </row>
     <row r="3">
@@ -578,44 +544,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>组织安全培训演练</t>
+          <t>完成年度预算编制</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
+        <v>46</v>
+      </c>
+      <c r="E3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F3" t="n">
         <v>18</v>
       </c>
-      <c r="E3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F3" t="n">
-        <v>20</v>
-      </c>
       <c r="G3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>46</v>
+      </c>
+      <c r="J3" t="n">
+        <v>36</v>
+      </c>
+      <c r="K3" t="n">
         <v>10</v>
       </c>
-      <c r="I3" t="n">
-        <v>40</v>
-      </c>
-      <c r="J3" t="n">
-        <v>19</v>
-      </c>
-      <c r="K3" t="n">
-        <v>45</v>
-      </c>
       <c r="L3" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="M3" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O3">
         <f>SUM(C3:N3)</f>
@@ -623,51 +589,46 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>综合办公室</t>
-        </is>
-      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>设备巡检维护</t>
+          <t>组织安全培训演练</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="H4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J4" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="L4" t="n">
+        <v>47</v>
+      </c>
+      <c r="M4" t="n">
+        <v>38</v>
+      </c>
+      <c r="N4" t="n">
         <v>18</v>
-      </c>
-      <c r="M4" t="n">
-        <v>48</v>
-      </c>
-      <c r="N4" t="n">
-        <v>33</v>
       </c>
       <c r="O4">
         <f>SUM(C4:N4)</f>
@@ -675,51 +636,46 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>综合办公室</t>
-        </is>
-      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>季度报表汇总</t>
+          <t>设备巡检维护</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>22</v>
+      </c>
+      <c r="I5" t="n">
+        <v>34</v>
+      </c>
+      <c r="J5" t="n">
+        <v>31</v>
+      </c>
+      <c r="K5" t="n">
+        <v>22</v>
+      </c>
+      <c r="L5" t="n">
         <v>18</v>
       </c>
-      <c r="G5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H5" t="n">
-        <v>50</v>
-      </c>
-      <c r="I5" t="n">
-        <v>42</v>
-      </c>
-      <c r="J5" t="n">
-        <v>42</v>
-      </c>
-      <c r="K5" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>37</v>
-      </c>
       <c r="M5" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="N5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O5">
         <f>SUM(C5:N5)</f>
@@ -727,51 +683,46 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>财务部</t>
-        </is>
-      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>组织安全培训演练</t>
+          <t>季度报表汇总</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="D6" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="O6">
         <f>SUM(C6:N6)</f>
@@ -786,44 +737,44 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>设备巡检维护</t>
+          <t>组织安全培训演练</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="D7" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G7" t="n">
+        <v>24</v>
+      </c>
+      <c r="H7" t="n">
+        <v>41</v>
+      </c>
+      <c r="I7" t="n">
+        <v>43</v>
+      </c>
+      <c r="J7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K7" t="n">
         <v>10</v>
       </c>
-      <c r="F7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G7" t="n">
-        <v>49</v>
-      </c>
-      <c r="H7" t="n">
-        <v>17</v>
-      </c>
-      <c r="I7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>40</v>
-      </c>
-      <c r="K7" t="n">
-        <v>30</v>
-      </c>
       <c r="L7" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="N7" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="O7">
         <f>SUM(C7:N7)</f>
@@ -831,51 +782,46 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>财务部</t>
-        </is>
-      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>季度报表汇总</t>
+          <t>设备巡检维护</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" t="n">
+        <v>48</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
         <v>30</v>
       </c>
-      <c r="D8" t="n">
-        <v>44</v>
-      </c>
-      <c r="E8" t="n">
-        <v>13</v>
-      </c>
-      <c r="F8" t="n">
-        <v>48</v>
-      </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="H8" t="n">
+        <v>17</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>40</v>
+      </c>
+      <c r="K8" t="n">
         <v>30</v>
       </c>
-      <c r="I8" t="n">
-        <v>30</v>
-      </c>
-      <c r="J8" t="n">
-        <v>18</v>
-      </c>
-      <c r="K8" t="n">
-        <v>46</v>
-      </c>
       <c r="L8" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="M8" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O8">
         <f>SUM(C8:N8)</f>
@@ -883,51 +829,46 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>财务部</t>
-        </is>
-      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>完成资料汇总</t>
+          <t>季度报表汇总</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E9" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" t="n">
         <v>18</v>
       </c>
-      <c r="J9" t="n">
-        <v>6</v>
-      </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="L9" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="M9" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="O9">
         <f>SUM(C9:N9)</f>
@@ -935,51 +876,46 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>工程技术部</t>
-        </is>
-      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>设备巡检维护</t>
+          <t>完成资料汇总</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E10" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H10" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="N10" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <f>SUM(C10:N10)</f>
@@ -994,44 +930,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>季度报表汇总</t>
+          <t>设备巡检维护</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D11" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J11" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="L11" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="M11" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="O11">
         <f>SUM(C11:N11)</f>
@@ -1039,51 +975,46 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>工程技术部</t>
-        </is>
-      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>完成资料汇总</t>
+          <t>季度报表汇总</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E12" t="n">
+        <v>36</v>
+      </c>
+      <c r="F12" t="n">
+        <v>41</v>
+      </c>
+      <c r="G12" t="n">
+        <v>15</v>
+      </c>
+      <c r="H12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>49</v>
+      </c>
+      <c r="K12" t="n">
         <v>48</v>
       </c>
-      <c r="F12" t="n">
-        <v>33</v>
-      </c>
-      <c r="G12" t="n">
-        <v>39</v>
-      </c>
-      <c r="H12" t="n">
-        <v>49</v>
-      </c>
-      <c r="I12" t="n">
-        <v>19</v>
-      </c>
-      <c r="J12" t="n">
-        <v>29</v>
-      </c>
-      <c r="K12" t="n">
-        <v>35</v>
-      </c>
       <c r="L12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="O12">
         <f>SUM(C12:N12)</f>
@@ -1091,58 +1022,162 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>工程技术部</t>
-        </is>
-      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>成本合计核算</t>
+          <t>完成资料汇总</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="F13" t="n">
+        <v>33</v>
+      </c>
+      <c r="G13" t="n">
+        <v>39</v>
+      </c>
+      <c r="H13" t="n">
+        <v>49</v>
+      </c>
+      <c r="I13" t="n">
+        <v>19</v>
+      </c>
+      <c r="J13" t="n">
+        <v>29</v>
+      </c>
+      <c r="K13" t="n">
         <v>35</v>
       </c>
-      <c r="G13" t="n">
-        <v>36</v>
-      </c>
-      <c r="H13" t="n">
-        <v>12</v>
-      </c>
-      <c r="I13" t="n">
-        <v>47</v>
-      </c>
-      <c r="J13" t="n">
-        <v>10</v>
-      </c>
-      <c r="K13" t="n">
-        <v>29</v>
-      </c>
       <c r="L13" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="M13" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="N13" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="O13">
         <f>SUM(C13:N13)</f>
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>成本合计核算</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>45</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>22</v>
+      </c>
+      <c r="F14" t="n">
+        <v>35</v>
+      </c>
+      <c r="G14" t="n">
+        <v>36</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="n">
+        <v>47</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="n">
+        <v>29</v>
+      </c>
+      <c r="L14" t="n">
+        <v>40</v>
+      </c>
+      <c r="M14" t="n">
+        <v>29</v>
+      </c>
+      <c r="N14" t="n">
+        <v>42</v>
+      </c>
+      <c r="O14">
+        <f>SUM(C14:N14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>SUM(C3:C14)</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>SUM(D3:D14)</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>SUM(E3:E14)</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>SUM(F3:F14)</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>SUM(G3:G14)</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>SUM(H3:H14)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>SUM(I3:I14)</f>
+        <v/>
+      </c>
+      <c r="J15">
+        <f>SUM(J3:J14)</f>
+        <v/>
+      </c>
+      <c r="K15">
+        <f>SUM(K3:K14)</f>
+        <v/>
+      </c>
+      <c r="L15">
+        <f>SUM(L3:L14)</f>
+        <v/>
+      </c>
+      <c r="M15">
+        <f>SUM(M3:M14)</f>
+        <v/>
+      </c>
+      <c r="N15">
+        <f>SUM(N3:N14)</f>
+        <v/>
+      </c>
+      <c r="O15">
+        <f>SUM(O3:O14)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>